--- a/DAXRLAB1.xlsx
+++ b/DAXRLAB1.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CHETHAN SURESH\Desktop\Temp sunil\project\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BEE5FD9-DC14-4A99-9754-77FE38DD6628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E0D97F5B-7100-4735-A045-AB5D7E1BDFC0}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Chart1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
   <si>
     <t>USN</t>
   </si>
@@ -398,12 +392,15 @@
   </si>
   <si>
     <t>O</t>
+  </si>
+  <si>
+    <t>CREADITS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -439,8 +436,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,9 +460,9 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-IN"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -519,11 +520,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1946024992"/>
-        <c:axId val="1946024512"/>
+        <c:axId val="131212800"/>
+        <c:axId val="136679936"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1946024992"/>
+        <c:axId val="131212800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -565,7 +566,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1946024512"/>
+        <c:crossAx val="136679936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -573,7 +574,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1946024512"/>
+        <c:axId val="136679936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -623,7 +624,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1946024992"/>
+        <c:crossAx val="131212800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -638,7 +639,7 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
@@ -1218,7 +1219,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{F5B43415-2D89-470A-A3CA-0D505C243A05}">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1235,7 +1236,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C07F0F02-46CA-5E72-2E4A-3219D300DDD4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C07F0F02-46CA-5E72-2E4A-3219D300DDD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1547,21 +1548,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91838E9A-E124-4C0B-A346-821F96AD7115}">
-  <dimension ref="A3:U103"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:W104"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M3" t="s">
         <v>112</v>
@@ -1613,620 +1616,1699 @@
       <c r="U3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="W3" t="str">
+        <f ca="1">IF(OR(K5&lt;85, J5&lt;40),"NE",IF(J5&gt;=90,"O",IF(J5&gt;=80,"A+",IF(J5&gt;=70,"A",IF(J5&gt;=60,"B+",IF(J5&gt;=55,"B",IF(J5&gt;=50,"C",IF(J5&gt;=40,"P","F"))))))))</f>
+        <v>NE</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <f ca="1">RANDBETWEEN(0,100)</f>
+        <v>54</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ref="D5:H20" ca="1" si="0">RANDBETWEEN(0,100)</f>
+        <v>45</v>
+      </c>
+      <c r="E5">
+        <f ca="1">RANDBETWEEN(0,100)</f>
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <f ca="1">RANDBETWEEN(0,100)</f>
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <f t="shared" ca="1" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="I5">
+        <f ca="1">SUM(C5:H5)</f>
+        <v>225</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" ref="J5:J31" ca="1" si="1">AVERAGE(C5:H5)</f>
+        <v>37.5</v>
+      </c>
+      <c r="K5">
+        <f ca="1">RANDBETWEEN(0,100)</f>
+        <v>44</v>
+      </c>
+      <c r="L5">
+        <f ca="1">VLOOKUP(J5,$S$5:$U$12,3,TRUE)*6</f>
+        <v>0</v>
+      </c>
+      <c r="M5" t="e">
+        <f>SUMPRODUCT($C$4:$H$4,VLOOKUP(C5:H5,$S$5:$V$12,3,TRUE))/SUM($C$4:$H$4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N5">
+        <f ca="1">SUM(E5,C5)</f>
+        <v>86</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" t="s">
+        <v>116</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:H31" ca="1" si="2">RANDBETWEEN(0,100)</f>
+        <v>70</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="G6">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="H6">
+        <f t="shared" ca="1" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="I6">
+        <f t="shared" ref="I6:I31" ca="1" si="3">SUM(C6:H6)</f>
+        <v>263</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>43.833333333333336</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ref="K6:K31" ca="1" si="4">RANDBETWEEN(0,100)</f>
+        <v>73</v>
+      </c>
+      <c r="L6">
+        <f t="shared" ref="L6:L30" ca="1" si="5">VLOOKUP(J6,$S$5:$U$12,3,TRUE)*6</f>
+        <v>24</v>
+      </c>
+      <c r="S6">
+        <v>40</v>
+      </c>
+      <c r="T6" t="s">
+        <v>117</v>
+      </c>
+      <c r="U6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ca="1" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ca="1" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ca="1" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F7">
+        <f t="shared" ca="1" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="G7">
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <f t="shared" ca="1" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="I7">
+        <f t="shared" ca="1" si="3"/>
+        <v>402</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ca="1" si="4"/>
+        <v>65</v>
+      </c>
+      <c r="L7">
+        <f t="shared" ca="1" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="S7">
+        <v>50</v>
+      </c>
+      <c r="T7" t="s">
+        <v>118</v>
+      </c>
+      <c r="U7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ca="1" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ca="1" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ca="1" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ca="1" si="3"/>
+        <v>242</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>40.333333333333336</v>
+      </c>
+      <c r="K8">
+        <f t="shared" ca="1" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="S8">
+        <v>55</v>
+      </c>
+      <c r="T8" t="s">
+        <v>119</v>
+      </c>
+      <c r="U8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
-        <f t="shared" ref="D4:H4" ca="1" si="0">RANDBETWEEN(0,100)</f>
+      <c r="C9">
+        <f t="shared" ca="1" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ca="1" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="F9">
+        <f t="shared" ca="1" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="G9">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="I9">
+        <f t="shared" ca="1" si="3"/>
+        <v>285</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>47.5</v>
+      </c>
+      <c r="K9">
+        <f t="shared" ca="1" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="S9">
+        <v>60</v>
+      </c>
+      <c r="T9" t="s">
+        <v>120</v>
+      </c>
+      <c r="U9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ca="1" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ca="1" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ca="1" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <f t="shared" ca="1" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="H10">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="I10">
+        <f t="shared" ca="1" si="3"/>
+        <v>372</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="K10">
+        <f t="shared" ca="1" si="4"/>
+        <v>44</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ca="1" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="S10">
         <v>70</v>
       </c>
-      <c r="E4">
-        <f t="shared" ca="1" si="0"/>
+      <c r="T10" t="s">
+        <v>121</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ca="1" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="F11">
+        <f t="shared" ca="1" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="G11">
+        <f t="shared" ca="1" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="H11">
+        <f t="shared" ca="1" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <f t="shared" ca="1" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>41.666666666666664</v>
+      </c>
+      <c r="K11">
+        <f t="shared" ca="1" si="4"/>
+        <v>58</v>
+      </c>
+      <c r="L11">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="S11">
+        <v>80</v>
+      </c>
+      <c r="T11" t="s">
+        <v>122</v>
+      </c>
+      <c r="U11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ca="1" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ca="1" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ca="1" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ca="1" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="H12">
+        <f t="shared" ca="1" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="I12">
+        <f t="shared" ca="1" si="3"/>
+        <v>412</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>68.666666666666671</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ca="1" si="4"/>
+        <v>93</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ca="1" si="5"/>
+        <v>42</v>
+      </c>
+      <c r="S12">
+        <v>90</v>
+      </c>
+      <c r="T12" t="s">
+        <v>123</v>
+      </c>
+      <c r="U12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ca="1" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ca="1" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="E13">
+        <f t="shared" ca="1" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="F13">
+        <f t="shared" ca="1" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="G13">
+        <f t="shared" ca="1" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="H13">
+        <f t="shared" ca="1" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="I13">
+        <f t="shared" ca="1" si="3"/>
+        <v>377</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>62.833333333333336</v>
+      </c>
+      <c r="K13">
+        <f t="shared" ca="1" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ca="1" si="5"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ca="1" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ca="1" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="F14">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <f t="shared" ca="1" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="H14">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="I14">
+        <f t="shared" ca="1" si="3"/>
+        <v>260</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>43.333333333333336</v>
+      </c>
+      <c r="K14">
+        <f t="shared" ca="1" si="4"/>
+        <v>74</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ca="1" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ca="1" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="F15">
+        <f t="shared" ca="1" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="H15">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <f t="shared" ca="1" si="3"/>
+        <v>276</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="K15">
+        <f t="shared" ca="1" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="L15">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <f t="shared" ca="1" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ca="1" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ca="1" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ca="1" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="H16">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ca="1" si="3"/>
+        <v>283</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>47.166666666666664</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ca="1" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ca="1" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ca="1" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ca="1" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="F17">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <f t="shared" ca="1" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="H17">
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ca="1" si="3"/>
+        <v>333</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>55.5</v>
+      </c>
+      <c r="K17">
+        <f t="shared" ca="1" si="4"/>
+        <v>21</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ca="1" si="5"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ca="1" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ca="1" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="F18">
+        <f t="shared" ca="1" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ca="1" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ca="1" si="3"/>
+        <v>263</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>43.833333333333336</v>
+      </c>
+      <c r="K18">
+        <f t="shared" ca="1" si="4"/>
+        <v>82</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ca="1" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ca="1" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="E19">
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="F19">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="H19">
+        <f t="shared" ca="1" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ca="1" si="3"/>
+        <v>258</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="K19">
+        <f t="shared" ca="1" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <f t="shared" ca="1" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ca="1" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ca="1" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="F20">
+        <f t="shared" ca="1" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="G20">
+        <f t="shared" ca="1" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ca="1" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="I20">
+        <f t="shared" ca="1" si="3"/>
+        <v>378</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="K20">
+        <f t="shared" ca="1" si="4"/>
+        <v>62</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ca="1" si="5"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21">
+        <f t="shared" ca="1" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="D21">
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ca="1" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F21">
+        <f t="shared" ca="1" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="G21">
+        <f t="shared" ca="1" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="H21">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <f t="shared" ca="1" si="3"/>
+        <v>237</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>39.5</v>
+      </c>
+      <c r="K21">
+        <f t="shared" ca="1" si="4"/>
+        <v>42</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <f t="shared" ca="1" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="D22">
+        <f t="shared" ca="1" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="E22">
+        <f t="shared" ca="1" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ca="1" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <f t="shared" ca="1" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="H22">
+        <f t="shared" ca="1" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="I22">
+        <f t="shared" ca="1" si="3"/>
+        <v>316</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>52.666666666666664</v>
+      </c>
+      <c r="K22">
+        <f t="shared" ca="1" si="4"/>
+        <v>39</v>
+      </c>
+      <c r="L22">
+        <f t="shared" ca="1" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23">
+        <f t="shared" ca="1" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="D23">
+        <f t="shared" ca="1" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="E23">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ca="1" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="G23">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="H23">
+        <f t="shared" ca="1" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="I23">
+        <f t="shared" ca="1" si="3"/>
+        <v>238</v>
+      </c>
+      <c r="J23" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>39.666666666666664</v>
+      </c>
+      <c r="K23">
+        <f t="shared" ca="1" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="L23">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24">
+        <f t="shared" ca="1" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="D24">
+        <f t="shared" ca="1" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="F24">
+        <f t="shared" ca="1" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="G24">
+        <f t="shared" ca="1" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H24">
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="I24">
+        <f t="shared" ca="1" si="3"/>
+        <v>211</v>
+      </c>
+      <c r="J24" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>35.166666666666664</v>
+      </c>
+      <c r="K24">
+        <f t="shared" ca="1" si="4"/>
+        <v>87</v>
+      </c>
+      <c r="L24">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ca="1" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="E25">
+        <f t="shared" ca="1" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="F25">
+        <f t="shared" ca="1" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="G25">
+        <f t="shared" ca="1" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="H25">
+        <f t="shared" ca="1" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="I25">
+        <f t="shared" ca="1" si="3"/>
+        <v>206</v>
+      </c>
+      <c r="J25" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>34.333333333333336</v>
+      </c>
+      <c r="K25">
+        <f t="shared" ca="1" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="L25">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ca="1" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ca="1" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ca="1" si="2"/>
+        <v>59</v>
+      </c>
+      <c r="F26">
+        <f t="shared" ca="1" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="G26">
+        <f t="shared" ca="1" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="H26">
+        <f t="shared" ca="1" si="2"/>
         <v>44</v>
       </c>
-      <c r="F4">
-        <f t="shared" ca="1" si="0"/>
+      <c r="I26">
+        <f t="shared" ca="1" si="3"/>
+        <v>195</v>
+      </c>
+      <c r="J26" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>32.5</v>
+      </c>
+      <c r="K26">
+        <f t="shared" ca="1" si="4"/>
+        <v>97</v>
+      </c>
+      <c r="L26">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27">
+        <f t="shared" ca="1" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="D27">
+        <f t="shared" ca="1" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E27">
+        <f t="shared" ca="1" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="F27">
+        <f t="shared" ca="1" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="G27">
+        <f t="shared" ca="1" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="H27">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <f t="shared" ca="1" si="3"/>
+        <v>275</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>45.833333333333336</v>
+      </c>
+      <c r="K27">
+        <f t="shared" ca="1" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="L27">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <f t="shared" ca="1" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="D28">
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ca="1" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="F28">
+        <f t="shared" ca="1" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="G28">
+        <f t="shared" ca="1" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="H28">
+        <f t="shared" ca="1" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="I28">
+        <f t="shared" ca="1" si="3"/>
+        <v>358</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>59.666666666666664</v>
+      </c>
+      <c r="K28">
+        <f t="shared" ca="1" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="L28">
+        <f t="shared" ca="1" si="5"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29">
+        <f t="shared" ca="1" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <f t="shared" ca="1" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ca="1" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="F29">
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="G29">
+        <f t="shared" ca="1" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="H29">
+        <f t="shared" ca="1" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="I29">
+        <f t="shared" ca="1" si="3"/>
+        <v>162</v>
+      </c>
+      <c r="J29" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="K29">
+        <f t="shared" ca="1" si="4"/>
+        <v>90</v>
+      </c>
+      <c r="L29">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30">
+        <f t="shared" ca="1" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ca="1" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ca="1" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="F30">
+        <f t="shared" ca="1" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="G30">
+        <f t="shared" ca="1" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="H30">
+        <f t="shared" ca="1" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="I30">
+        <f t="shared" ca="1" si="3"/>
+        <v>343</v>
+      </c>
+      <c r="J30" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>57.166666666666664</v>
+      </c>
+      <c r="K30">
+        <f t="shared" ca="1" si="4"/>
+        <v>76</v>
+      </c>
+      <c r="L30">
+        <f t="shared" ca="1" si="5"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31">
+        <f t="shared" ca="1" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="D31">
+        <f t="shared" ca="1" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="E31">
+        <f t="shared" ca="1" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="F31">
+        <f t="shared" ca="1" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="G31">
+        <f t="shared" ca="1" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="H31">
+        <f t="shared" ca="1" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="I31">
+        <f t="shared" ca="1" si="3"/>
+        <v>274</v>
+      </c>
+      <c r="J31" s="2">
+        <f t="shared" ca="1" si="1"/>
+        <v>45.666666666666664</v>
+      </c>
+      <c r="K31">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="L31">
+        <f t="shared" ref="L6:L31" ca="1" si="6">VLOOKUP(J31,$S$5:$U$12,3,TRUE)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="14.45" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>65</v>
       </c>
-      <c r="G4">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="I4">
-        <f ca="1">SUM(C4:H4)</f>
-        <v>255</v>
-      </c>
-      <c r="J4">
-        <f ca="1">AVERAGE(C4:H4)</f>
-        <v>42.5</v>
-      </c>
-      <c r="K4">
-        <f ca="1">RANDBETWEEN(0,100)</f>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>81</v>
       </c>
-      <c r="L4" t="str">
-        <f ca="1">VLOOKUP(J4,$S$4:$U$11,2,TRUE)</f>
-        <v>P</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4" t="s">
-        <v>116</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5">
-        <v>40</v>
-      </c>
-      <c r="T5" t="s">
-        <v>117</v>
-      </c>
-      <c r="U5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="S6">
-        <v>50</v>
-      </c>
-      <c r="T6" t="s">
-        <v>118</v>
-      </c>
-      <c r="U6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="S7">
-        <v>55</v>
-      </c>
-      <c r="T7" t="s">
-        <v>119</v>
-      </c>
-      <c r="U7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="S8">
-        <v>60</v>
-      </c>
-      <c r="T8" t="s">
-        <v>120</v>
-      </c>
-      <c r="U8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="S9">
-        <v>70</v>
-      </c>
-      <c r="T9" t="s">
-        <v>121</v>
-      </c>
-      <c r="U9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="S10">
-        <v>80</v>
-      </c>
-      <c r="T10" t="s">
-        <v>122</v>
-      </c>
-      <c r="U10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11">
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>90</v>
       </c>
-      <c r="T11" t="s">
-        <v>123</v>
-      </c>
-      <c r="U11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>107</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:B4"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
